--- a/scripts/fixtures/long_term_growth_journal.xlsx
+++ b/scripts/fixtures/long_term_growth_journal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/momacbookair/Library/Mobile Documents/com~apple~CloudDocs/CanSlim/Trading Journal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AFC582-70A9-AB47-A15B-13301D83C26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CE6A3E-D7B3-9F40-BAF1-0404F54F72AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66980" yWindow="4360" windowWidth="26040" windowHeight="14680" xr2:uid="{1F9C930A-3A9E-B645-8710-87EE27351EDC}"/>
+    <workbookView xWindow="54720" yWindow="280" windowWidth="45380" windowHeight="28120" xr2:uid="{1F9C930A-3A9E-B645-8710-87EE27351EDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -76,12 +76,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,13 +103,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -439,13 +449,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B72C3F-8163-3F4F-95CF-ECC84D9D8D92}">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -886,7 +897,7 @@
         <v>23039.690000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>46121</v>
       </c>
@@ -900,7 +911,7 @@
         <v>24104.36</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>46120</v>
       </c>
@@ -914,7 +925,7 @@
         <v>23645.690000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>46119</v>
       </c>
@@ -928,7 +939,7 @@
         <v>21043.27</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>46118</v>
       </c>
@@ -939,7 +950,7 @@
         <v>17714.16</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>46114</v>
       </c>
@@ -953,8 +964,8 @@
         <v>18787.54</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="7">
         <v>46113</v>
       </c>
       <c r="B38" s="2">
@@ -964,697 +975,198 @@
         <v>15698.43</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="5">
         <v>46112</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="4">
         <v>14681.619999999999</v>
       </c>
-      <c r="D39" s="2">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4">
         <v>14681.619999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>46111</v>
-      </c>
-      <c r="B40" s="2">
-        <v>13374.380000000001</v>
-      </c>
-      <c r="D40" s="2">
-        <v>13374.380000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>46108</v>
-      </c>
-      <c r="B41" s="2">
-        <v>13885.61</v>
-      </c>
-      <c r="D41" s="2">
-        <v>13885.61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>46107</v>
-      </c>
-      <c r="B42" s="2">
-        <v>14611.21</v>
-      </c>
-      <c r="D42" s="2">
-        <v>14611.21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
-        <v>46106</v>
-      </c>
-      <c r="B43" s="2">
-        <v>17036.14</v>
-      </c>
-      <c r="D43" s="2">
-        <v>17036.14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>46105</v>
-      </c>
-      <c r="B44" s="2">
-        <v>14081.61</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2880</v>
-      </c>
-      <c r="D44" s="2">
-        <v>16961.61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>46104</v>
-      </c>
-      <c r="B45" s="2">
-        <v>14206.919999999998</v>
-      </c>
-      <c r="D45" s="2">
-        <v>14206.919999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>46101</v>
-      </c>
-      <c r="B46" s="2">
-        <v>14076.25</v>
-      </c>
-      <c r="D46" s="2">
-        <v>14076.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>46100</v>
-      </c>
-      <c r="B47" s="2">
-        <v>15503</v>
-      </c>
-      <c r="D47" s="2">
-        <v>15503</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>46099</v>
-      </c>
-      <c r="B48" s="2">
-        <v>16048.970000000001</v>
-      </c>
-      <c r="D48" s="2">
-        <v>16048.970000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>46098</v>
-      </c>
-      <c r="B49" s="2">
-        <v>13334.720000000001</v>
-      </c>
-      <c r="C49" s="2">
-        <v>2690</v>
-      </c>
-      <c r="D49" s="2">
-        <v>16024.720000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>46097</v>
-      </c>
-      <c r="B50" s="2">
-        <v>12968.099999999999</v>
-      </c>
-      <c r="D50" s="2">
-        <v>12968.099999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>46094</v>
-      </c>
-      <c r="B51" s="2">
-        <v>12705.599999999999</v>
-      </c>
-      <c r="D51" s="2">
-        <v>12705.599999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
-        <v>46093</v>
-      </c>
-      <c r="B52" s="2">
-        <v>13008.25</v>
-      </c>
-      <c r="D52" s="2">
-        <v>13008.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
-        <v>46092</v>
-      </c>
-      <c r="B53" s="2">
-        <v>13140.400000000001</v>
-      </c>
-      <c r="D53" s="2">
-        <v>13140.400000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
-        <v>46091</v>
-      </c>
-      <c r="B54" s="2">
-        <v>13154.349999999999</v>
-      </c>
-      <c r="D54" s="2">
-        <v>13154.349999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
-        <v>46090</v>
-      </c>
-      <c r="B55" s="2">
-        <v>13114.150000000001</v>
-      </c>
-      <c r="D55" s="2">
-        <v>13114.150000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
-        <v>46087</v>
-      </c>
-      <c r="B56" s="2">
-        <v>12891.099999999999</v>
-      </c>
-      <c r="D56" s="2">
-        <v>12891.099999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B57" s="2">
-        <v>13958.620000000003</v>
-      </c>
-      <c r="D57" s="2">
-        <v>13958.620000000003</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
-        <v>46085</v>
-      </c>
-      <c r="B58" s="2">
-        <v>14293.620000000003</v>
-      </c>
-      <c r="D58" s="2">
-        <v>14293.620000000003</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
-        <v>46084</v>
-      </c>
-      <c r="B59" s="2">
-        <v>13180.720000000001</v>
-      </c>
-      <c r="D59" s="2">
-        <v>13180.720000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
-        <v>46083</v>
-      </c>
-      <c r="B60" s="2">
-        <v>14141.269999999997</v>
-      </c>
-      <c r="D60" s="2">
-        <v>14141.269999999997</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
-        <v>46080</v>
-      </c>
-      <c r="B61" s="2">
-        <v>13928.769999999997</v>
-      </c>
-      <c r="D61" s="2">
-        <v>13928.769999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
-        <v>46079</v>
-      </c>
-      <c r="B62" s="2">
-        <v>15752.29</v>
-      </c>
-      <c r="D62" s="2">
-        <v>15752.29</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
-        <v>46078</v>
-      </c>
-      <c r="B63" s="2">
-        <v>16381.660000000003</v>
-      </c>
-      <c r="D63" s="2">
-        <v>16381.660000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
-        <v>46077</v>
-      </c>
-      <c r="B64" s="2">
-        <v>15159.989999999998</v>
-      </c>
-      <c r="D64" s="2">
-        <v>15159.989999999998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
-        <v>46076</v>
-      </c>
-      <c r="B65" s="2">
-        <v>14064</v>
-      </c>
-      <c r="D65" s="2">
-        <v>14064</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
-        <v>46073</v>
-      </c>
-      <c r="B66" s="2">
-        <v>11978.730000000003</v>
-      </c>
-      <c r="C66" s="2">
-        <v>2880</v>
-      </c>
-      <c r="D66" s="2">
-        <v>14858.730000000003</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
-        <v>46072</v>
-      </c>
-      <c r="B67" s="2">
-        <v>10098.480000000003</v>
-      </c>
-      <c r="C67" s="2">
-        <v>2810</v>
-      </c>
-      <c r="D67" s="2">
-        <v>12908.480000000003</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
-        <v>46071</v>
-      </c>
-      <c r="B68" s="2">
-        <v>8107.5800000000017</v>
-      </c>
-      <c r="D68" s="2">
-        <v>8107.5800000000017</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
-        <v>46070</v>
-      </c>
-      <c r="B69" s="2">
-        <v>8190.0800000000017</v>
-      </c>
-      <c r="D69" s="2">
-        <v>8190.0800000000017</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
-        <v>46066</v>
-      </c>
-      <c r="B70" s="2">
-        <v>9405.0800000000017</v>
-      </c>
-      <c r="D70" s="2">
-        <v>9405.0800000000017</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
-        <v>46065</v>
-      </c>
-      <c r="B71" s="2">
-        <v>9292.5800000000017</v>
-      </c>
-      <c r="D71" s="2">
-        <v>9292.5800000000017</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
-        <v>46064</v>
-      </c>
-      <c r="B72" s="2">
-        <v>12733.93</v>
-      </c>
-      <c r="D72" s="2">
-        <v>12733.93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
-        <v>46063</v>
-      </c>
-      <c r="B73" s="2">
-        <v>13255.510000000002</v>
-      </c>
-      <c r="D73" s="2">
-        <v>13255.510000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
-        <v>46062</v>
-      </c>
-      <c r="B74" s="2">
-        <v>14334.010000000002</v>
-      </c>
-      <c r="D74" s="2">
-        <v>14334.010000000002</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>46059</v>
-      </c>
-      <c r="B75" s="2">
-        <v>12149.510000000002</v>
-      </c>
-      <c r="D75" s="2">
-        <v>12149.510000000002</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
-        <v>46058</v>
-      </c>
-      <c r="B76" s="2">
-        <v>8698.010000000002</v>
-      </c>
-      <c r="D76" s="2">
-        <v>8698.010000000002</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
-        <v>46057</v>
-      </c>
-      <c r="B77" s="2">
-        <v>10656.510000000002</v>
-      </c>
-      <c r="D77" s="2">
-        <v>10656.510000000002</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
-        <v>46056</v>
-      </c>
-      <c r="B78" s="2">
-        <v>12999.550000000003</v>
-      </c>
-      <c r="D78" s="2">
-        <v>12999.550000000003</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
-        <v>46055</v>
-      </c>
-      <c r="B79" s="2">
-        <v>12334.919999999998</v>
-      </c>
-      <c r="D79" s="2">
-        <v>12334.919999999998</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
-        <v>46052</v>
-      </c>
-      <c r="B80" s="2">
-        <v>13825.300000000003</v>
-      </c>
-      <c r="D80" s="2">
-        <v>13825.300000000003</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>46051</v>
-      </c>
-      <c r="B81" s="2">
-        <v>15571.349999999999</v>
-      </c>
-      <c r="D81" s="2">
-        <v>15571.349999999999</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>46050</v>
-      </c>
-      <c r="B82" s="2">
-        <v>18569.04</v>
-      </c>
-      <c r="D82" s="2">
-        <v>18569.04</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
-        <v>46049</v>
-      </c>
-      <c r="B83" s="2">
-        <v>17318.120000000003</v>
-      </c>
-      <c r="D83" s="2">
-        <v>17318.120000000003</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>46048</v>
-      </c>
-      <c r="B84" s="2">
-        <v>9985.5600000000049</v>
-      </c>
-      <c r="C84" s="2">
-        <v>6347.42</v>
-      </c>
-      <c r="D84" s="2">
-        <v>16332.980000000005</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
-        <v>46045</v>
-      </c>
-      <c r="B85" s="2">
-        <v>12486.529999999999</v>
-      </c>
-      <c r="D85" s="2">
-        <v>12486.529999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
-        <v>46044</v>
-      </c>
-      <c r="B86" s="2">
-        <v>12518.029999999999</v>
-      </c>
-      <c r="D86" s="2">
-        <v>12518.029999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>46043</v>
-      </c>
-      <c r="B87" s="2">
-        <v>12057.529999999999</v>
-      </c>
-      <c r="D87" s="2">
-        <v>12057.529999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>46042</v>
-      </c>
-      <c r="B88" s="2">
-        <v>12056.520000000004</v>
-      </c>
-      <c r="D88" s="2">
-        <v>12056.520000000004</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>46038</v>
-      </c>
-      <c r="B89" s="2">
-        <v>13740.810000000005</v>
-      </c>
-      <c r="D89" s="2">
-        <v>13740.810000000005</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>46037</v>
-      </c>
-      <c r="B90" s="2">
-        <v>13255.630000000005</v>
-      </c>
-      <c r="D90" s="2">
-        <v>13255.630000000005</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
-        <v>46036</v>
-      </c>
-      <c r="B91" s="2">
-        <v>5125.5500000000029</v>
-      </c>
-      <c r="C91" s="2">
-        <v>9132.58</v>
-      </c>
-      <c r="D91" s="2">
-        <v>14258.130000000003</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
-        <v>46035</v>
-      </c>
-      <c r="B92" s="2">
-        <v>4741.9199999999983</v>
-      </c>
-      <c r="D92" s="2">
-        <v>4741.9199999999983</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
-        <v>46034</v>
-      </c>
-      <c r="B93" s="2">
-        <v>0</v>
-      </c>
-      <c r="C93" s="2">
-        <v>4850</v>
-      </c>
-      <c r="D93" s="2">
-        <v>4850</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>46031</v>
-      </c>
-      <c r="B94" s="2">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
-        <v>46030</v>
-      </c>
-      <c r="B95" s="2">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>46029</v>
-      </c>
-      <c r="B96" s="2">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
-        <v>46028</v>
-      </c>
-      <c r="B97" s="2">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
-        <v>46027</v>
-      </c>
-      <c r="B98" s="2">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
-        <v>46024</v>
-      </c>
-      <c r="B99" s="2">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2">
-        <v>0</v>
-      </c>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="3"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" s="3"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" s="3"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" s="3"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" s="3"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" s="3"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" s="3"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" s="3"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" s="3"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
